--- a/artfynd/A 21663-2024 artfynd.xlsx
+++ b/artfynd/A 21663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119290716</v>
+        <v>119290714</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630185</v>
+        <v>630135</v>
       </c>
       <c r="R2" t="n">
-        <v>7205437</v>
+        <v>7205168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119290721</v>
+        <v>119290715</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630164</v>
+        <v>630215</v>
       </c>
       <c r="R3" t="n">
-        <v>7205381</v>
+        <v>7205419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119290723</v>
+        <v>119290716</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630134</v>
+        <v>630185</v>
       </c>
       <c r="R4" t="n">
-        <v>7205388</v>
+        <v>7205437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119290715</v>
+        <v>119290717</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630215</v>
+        <v>630062</v>
       </c>
       <c r="R5" t="n">
-        <v>7205419</v>
+        <v>7205336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119290727</v>
+        <v>119290719</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630100</v>
+        <v>630103</v>
       </c>
       <c r="R6" t="n">
-        <v>7205309</v>
+        <v>7205261</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119290719</v>
+        <v>119290720</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630103</v>
+        <v>630124</v>
       </c>
       <c r="R7" t="n">
-        <v>7205261</v>
+        <v>7205191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119290724</v>
+        <v>119290721</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630094</v>
+        <v>630164</v>
       </c>
       <c r="R8" t="n">
-        <v>7205300</v>
+        <v>7205381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119290726</v>
+        <v>119290723</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630102</v>
+        <v>630134</v>
       </c>
       <c r="R9" t="n">
-        <v>7205281</v>
+        <v>7205388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119290720</v>
+        <v>119290724</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630124</v>
+        <v>630094</v>
       </c>
       <c r="R10" t="n">
-        <v>7205191</v>
+        <v>7205300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119290728</v>
+        <v>119290726</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630104</v>
+        <v>630102</v>
       </c>
       <c r="R11" t="n">
-        <v>7205302</v>
+        <v>7205281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119290717</v>
+        <v>119290727</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630062</v>
+        <v>630100</v>
       </c>
       <c r="R12" t="n">
-        <v>7205336</v>
+        <v>7205309</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,6 +1744,103 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119290728</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>630104</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7205302</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
